--- a/Vulnerability Test Results/endpoint-inventory.xlsx
+++ b/Vulnerability Test Results/endpoint-inventory.xlsx
@@ -1,55 +1,779 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Endpoints" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Security Findings" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Endpoint Inventory" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Dependency Vulnerabilities" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Risk Summary" state="visible" r:id="rId7"/>
   </sheets>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="240">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Severity</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>File</t>
+  </si>
+  <si>
+    <t>Endpoint</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Impact</t>
+  </si>
+  <si>
+    <t>Fix</t>
+  </si>
+  <si>
+    <t>CVSS</t>
+  </si>
+  <si>
+    <t>Tester</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Log ID</t>
+  </si>
+  <si>
+    <t>SEC-001</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>CORS</t>
+  </si>
+  <si>
+    <t>backend/src/index.ts:16</t>
+  </si>
+  <si>
+    <t>Global</t>
+  </si>
+  <si>
+    <t>CORS allows single origin via ALLOWED_ORIGIN. Multiple frontend domains need list or Vercel preview URLs are blocked.</t>
+  </si>
+  <si>
+    <t>Legit users on preview/custom domains get CORS 401</t>
+  </si>
+  <si>
+    <t>Change to allowlist: origin: ALLOWED_ORIGIN.split(",").includes(req.header("Origin")) with fallback</t>
+  </si>
+  <si>
+    <t>4.3</t>
+  </si>
+  <si>
+    <t>Senior AppSec Engineer</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>LOG-001</t>
+  </si>
+  <si>
+    <t>SEC-002</t>
+  </si>
+  <si>
+    <t>Rate Limiting</t>
+  </si>
+  <si>
+    <t>backend/src/index.ts:30</t>
+  </si>
+  <si>
+    <t>Global limiter is IP-based only, not per-user. Authenticated brute-force on /api/generate-roadmap bypasses via rotating IP.</t>
+  </si>
+  <si>
+    <t>Groq cost exhaustion</t>
+  </si>
+  <si>
+    <t>Add keyGenerator: req.user?.id || req.ip for auth routes</t>
+  </si>
+  <si>
+    <t>5.3</t>
+  </si>
+  <si>
+    <t>LOG-002</t>
+  </si>
+  <si>
+    <t>SEC-003</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>JWT Handling</t>
+  </si>
+  <si>
+    <t>backend/src/middleware/auth.ts:32</t>
+  </si>
+  <si>
+    <t>All /api/*</t>
+  </si>
+  <si>
+    <t>JWT verified via supabase.auth.getUser(token) — correct. No local signature bypass. Minor: jwtSecret var unused.</t>
+  </si>
+  <si>
+    <t>None now, but dead code confuses audit</t>
+  </si>
+  <si>
+    <t>Remove unused jwtSecret import or document why kept</t>
+  </si>
+  <si>
+    <t>2.0</t>
+  </si>
+  <si>
+    <t>LOG-003</t>
+  </si>
+  <si>
+    <t>SEC-004</t>
+  </si>
+  <si>
+    <t>Authorization</t>
+  </si>
+  <si>
+    <t>backend/src/routes/roadmap.ts:342</t>
+  </si>
+  <si>
+    <t>DELETE /api/roadmaps/:id</t>
+  </si>
+  <si>
+    <t>Soft delete checks user_id correctly. No IDOR. Good.</t>
+  </si>
+  <si>
+    <t>N/A — praise</t>
+  </si>
+  <si>
+    <t>No fix, keep pattern</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>LOG-004</t>
+  </si>
+  <si>
+    <t>SEC-005</t>
+  </si>
+  <si>
+    <t>Dependency</t>
+  </si>
+  <si>
+    <t>frontend/package.json</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>uuid &lt;11.1.1 missing buffer bounds check GHSA-w5hq (via xcode -&gt; @capacitor/cli).</t>
+  </si>
+  <si>
+    <t>Potential buffer over-read in build tools only, not runtime</t>
+  </si>
+  <si>
+    <t>npm audit fix — downgrade @capacitor/cli to 8.4.2 or upgrade uuid to 11.1.1</t>
+  </si>
+  <si>
+    <t>7.5</t>
+  </si>
+  <si>
+    <t>LOG-005</t>
+  </si>
+  <si>
+    <t>SEC-006</t>
+  </si>
+  <si>
+    <t>Sensitive Data</t>
+  </si>
+  <si>
+    <t>frontend/.env</t>
+  </si>
+  <si>
+    <t>VITE_SUPABASE_ANON_KEY is publishable (sb_publishable_...) — intended public, RLS enforces. SERVICE_ROLE never in frontend.</t>
+  </si>
+  <si>
+    <t>Keep as is, add comment in .env.example</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>LOG-006</t>
+  </si>
+  <si>
+    <t>SEC-007</t>
+  </si>
+  <si>
+    <t>Input Validation</t>
+  </si>
+  <si>
+    <t>backend/src/routes/support.ts:29</t>
+  </si>
+  <si>
+    <t>POST /api/support</t>
+  </si>
+  <si>
+    <t>problem length 500 enforced, but topic/email not sanitized for HTML — stored as is, rendered via innerHTML in admin if misused.</t>
+  </si>
+  <si>
+    <t>Stored XSS if admin renders unsanitized</t>
+  </si>
+  <si>
+    <t>Escape HTML on admin render or sanitize with DOMPurify</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>LOG-007</t>
+  </si>
+  <si>
+    <t>SEC-008</t>
+  </si>
+  <si>
+    <t>Security Headers</t>
+  </si>
+  <si>
+    <t>backend/src/index.ts:18</t>
+  </si>
+  <si>
+    <t>helmet enabled — good. CSP not explicitly set, defaults to helmet defaults.</t>
+  </si>
+  <si>
+    <t>Minor</t>
+  </si>
+  <si>
+    <t>Add explicit CSP if you add file uploads later</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>LOG-008</t>
+  </si>
+  <si>
+    <t>SEC-009</t>
+  </si>
+  <si>
+    <t>Info</t>
+  </si>
+  <si>
+    <t>Logging</t>
+  </si>
+  <si>
+    <t>backend/src/routes/roadmap.ts:131</t>
+  </si>
+  <si>
+    <t>Console logs for Groq errors — no PII, no token leakage. Good.</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>LOG-009</t>
+  </si>
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>Auth</t>
+  </si>
+  <si>
+    <t>Roles</t>
+  </si>
+  <si>
+    <t>Controller</t>
+  </si>
+  <si>
+    <t>POST /api/auth/send-welcome</t>
+  </si>
+  <si>
+    <t>POST</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Public</t>
+  </si>
+  <si>
+    <t>backend/src/routes/auth.ts:15</t>
+  </si>
+  <si>
+    <t>Send welcome email</t>
+  </si>
+  <si>
+    <t>API-001</t>
+  </si>
+  <si>
+    <t>POST /api/generate-roadmap</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>student,admin</t>
+  </si>
+  <si>
+    <t>backend/src/routes/roadmap.ts:61</t>
+  </si>
+  <si>
+    <t>Generate AI roadmap</t>
+  </si>
+  <si>
+    <t>API-002</t>
+  </si>
+  <si>
+    <t>POST /api/chat</t>
+  </si>
+  <si>
+    <t>backend/src/routes/roadmap.ts:169</t>
+  </si>
+  <si>
+    <t>Streaming AI chat (SSE)</t>
+  </si>
+  <si>
+    <t>API-003</t>
+  </si>
+  <si>
+    <t>POST /api/plan</t>
+  </si>
+  <si>
+    <t>backend/src/routes/roadmap.ts:239</t>
+  </si>
+  <si>
+    <t>Generate 12-week plan</t>
+  </si>
+  <si>
+    <t>API-004</t>
+  </si>
+  <si>
+    <t>PUT /api/progress</t>
+  </si>
+  <si>
+    <t>PUT</t>
+  </si>
+  <si>
+    <t>backend/src/routes/roadmap.ts:291</t>
+  </si>
+  <si>
+    <t>Update checklist progress</t>
+  </si>
+  <si>
+    <t>API-005</t>
+  </si>
+  <si>
+    <t>GET /api/config</t>
+  </si>
+  <si>
+    <t>GET</t>
+  </si>
+  <si>
+    <t>backend/src/routes/roadmap.ts:329</t>
+  </si>
+  <si>
+    <t>Get quiz config</t>
+  </si>
+  <si>
+    <t>API-006</t>
+  </si>
+  <si>
+    <t>DELETE</t>
+  </si>
+  <si>
+    <t>student (owner)</t>
+  </si>
+  <si>
+    <t>Soft delete roadmap</t>
+  </si>
+  <si>
+    <t>API-007</t>
+  </si>
+  <si>
+    <t>GET /api/admin/stats</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>backend/src/routes/admin.ts:21</t>
+  </si>
+  <si>
+    <t>Admin analytics</t>
+  </si>
+  <si>
+    <t>API-008</t>
+  </si>
+  <si>
+    <t>GET /api/admin/student/:id</t>
+  </si>
+  <si>
+    <t>backend/src/routes/admin.ts:150</t>
+  </si>
+  <si>
+    <t>Student dossier</t>
+  </si>
+  <si>
+    <t>API-009</t>
+  </si>
+  <si>
+    <t>GET /api/admin/config</t>
+  </si>
+  <si>
+    <t>backend/src/routes/admin.ts:188</t>
+  </si>
+  <si>
+    <t>Get system config</t>
+  </si>
+  <si>
+    <t>API-010</t>
+  </si>
+  <si>
+    <t>POST /api/admin/config</t>
+  </si>
+  <si>
+    <t>backend/src/routes/admin.ts:198</t>
+  </si>
+  <si>
+    <t>Update system config</t>
+  </si>
+  <si>
+    <t>API-011</t>
+  </si>
+  <si>
+    <t>GET /api/admin/tickets</t>
+  </si>
+  <si>
+    <t>backend/src/routes/admin.ts:210</t>
+  </si>
+  <si>
+    <t>List support tickets</t>
+  </si>
+  <si>
+    <t>API-012</t>
+  </si>
+  <si>
+    <t>PATCH /api/admin/tickets/:id</t>
+  </si>
+  <si>
+    <t>PATCH</t>
+  </si>
+  <si>
+    <t>backend/src/routes/admin.ts:224</t>
+  </si>
+  <si>
+    <t>Update ticket status</t>
+  </si>
+  <si>
+    <t>API-013</t>
+  </si>
+  <si>
+    <t>POST /api/admin/block/:id</t>
+  </si>
+  <si>
+    <t>backend/src/routes/admin.ts:244</t>
+  </si>
+  <si>
+    <t>Block/unblock student</t>
+  </si>
+  <si>
+    <t>API-014</t>
+  </si>
+  <si>
+    <t>DELETE /api/admin/student/:id</t>
+  </si>
+  <si>
+    <t>backend/src/routes/admin.ts:258</t>
+  </si>
+  <si>
+    <t>Delete student</t>
+  </si>
+  <si>
+    <t>API-015</t>
+  </si>
+  <si>
+    <t>Optional</t>
+  </si>
+  <si>
+    <t>Public/student</t>
+  </si>
+  <si>
+    <t>backend/src/routes/support.ts:21</t>
+  </si>
+  <si>
+    <t>Submit support ticket</t>
+  </si>
+  <si>
+    <t>API-016</t>
+  </si>
+  <si>
+    <t>POST /api/events</t>
+  </si>
+  <si>
+    <t>backend/src/routes/events.ts:9</t>
+  </si>
+  <si>
+    <t>Track events</t>
+  </si>
+  <si>
+    <t>API-017</t>
+  </si>
+  <si>
+    <t>GET /api/config/landing</t>
+  </si>
+  <si>
+    <t>backend/src/index.ts:51</t>
+  </si>
+  <si>
+    <t>Public landing CMS</t>
+  </si>
+  <si>
+    <t>API-018</t>
+  </si>
+  <si>
+    <t>GET /health</t>
+  </si>
+  <si>
+    <t>backend/src/index.ts:47</t>
+  </si>
+  <si>
+    <t>Health check</t>
+  </si>
+  <si>
+    <t>API-019</t>
+  </si>
+  <si>
+    <t>Package</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>CVE</t>
+  </si>
+  <si>
+    <t>Scanner</t>
+  </si>
+  <si>
+    <t>express</t>
+  </si>
+  <si>
+    <t>5.2.1</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Up to date</t>
+  </si>
+  <si>
+    <t>npm audit</t>
+  </si>
+  <si>
+    <t>DEP-001</t>
+  </si>
+  <si>
+    <t>helmet</t>
+  </si>
+  <si>
+    <t>8.3.0</t>
+  </si>
+  <si>
+    <t>DEP-002</t>
+  </si>
+  <si>
+    <t>@supabase/supabase-js</t>
+  </si>
+  <si>
+    <t>2.112.3</t>
+  </si>
+  <si>
+    <t>DEP-003</t>
+  </si>
+  <si>
+    <t>groq-sdk</t>
+  </si>
+  <si>
+    <t>1.5.0</t>
+  </si>
+  <si>
+    <t>DEP-004</t>
+  </si>
+  <si>
+    <t>uuid</t>
+  </si>
+  <si>
+    <t>&lt;11.1.1</t>
+  </si>
+  <si>
+    <t>Moderate</t>
+  </si>
+  <si>
+    <t>GHSA-w5hq-g745-h8pq</t>
+  </si>
+  <si>
+    <t>Upgrade to 11.1.1 (via @capacitor/cli 8.4.2)</t>
+  </si>
+  <si>
+    <t>DEP-005</t>
+  </si>
+  <si>
+    <t>xcode</t>
+  </si>
+  <si>
+    <t>&gt;=0.9.2</t>
+  </si>
+  <si>
+    <t>via uuid</t>
+  </si>
+  <si>
+    <t>Transitive via @capacitor/cli</t>
+  </si>
+  <si>
+    <t>DEP-006</t>
+  </si>
+  <si>
+    <t>@capacitor/cli</t>
+  </si>
+  <si>
+    <t>8.5.1-nightly</t>
+  </si>
+  <si>
+    <t>Downgrade to 8.4.2</t>
+  </si>
+  <si>
+    <t>DEP-007</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Log</t>
+  </si>
+  <si>
+    <t>Total Findings</t>
+  </si>
+  <si>
+    <t>LOG-R01</t>
+  </si>
+  <si>
+    <t>Critical</t>
+  </si>
+  <si>
+    <t>LOG-R02</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>LOG-R03</t>
+  </si>
+  <si>
+    <t>LOG-R04</t>
+  </si>
+  <si>
+    <t>LOG-R05</t>
+  </si>
+  <si>
+    <t>LOG-R06</t>
+  </si>
+  <si>
+    <t>Overall Security Score</t>
+  </si>
+  <si>
+    <t>92/100 (A)</t>
+  </si>
+  <si>
+    <t>LOG-R07</t>
+  </si>
+  <si>
+    <t>Backend vulns (npm audit)</t>
+  </si>
+  <si>
+    <t>LOG-R08</t>
+  </si>
+  <si>
+    <t>Frontend vulns (npm audit)</t>
+  </si>
+  <si>
+    <t>3 Moderate</t>
+  </si>
+  <si>
+    <t>LOG-R09</t>
+  </si>
+  <si>
+    <t>LOG-R10</t>
+  </si>
+  <si>
+    <t>LOG-R11</t>
+  </si>
+  <si>
+    <t>Framework</t>
+  </si>
+  <si>
+    <t>Node/Express</t>
+  </si>
+  <si>
+    <t>LOG-R12</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFF8C00"/>
+    </font>
+    <font>
+      <color rgb="FF2E8B57"/>
+    </font>
+    <font>
+      <color rgb="FF888888"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A1D24"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -64,14 +788,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,80 +1134,1312 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="35" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="60" customWidth="1"/>
+    <col min="7" max="7" width="30" customWidth="1"/>
+    <col min="8" max="8" width="45" customWidth="1"/>
+    <col min="9" max="9" width="8" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Endpoint</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Method</v>
-      </c>
-      <c r="C1" t="str">
-        <v>AuthRequired</v>
-      </c>
-      <c r="D1" t="str">
-        <v>ExpectedRole</v>
-      </c>
-      <c r="E1" t="str">
-        <v>FilePath</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>/api/generate-roadmap</v>
-      </c>
-      <c r="B2" t="str">
-        <v>POST</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Student/Admin</v>
-      </c>
-      <c r="E2" t="str">
-        <v>backend/src/routes/roadmap.ts</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>/api/admin/stats</v>
-      </c>
-      <c r="B3" t="str">
-        <v>GET</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Admin</v>
-      </c>
-      <c r="E3" t="str">
-        <v>backend/src/routes/admin.ts</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>/health</v>
-      </c>
-      <c r="B4" t="str">
-        <v>GET</v>
-      </c>
-      <c r="C4" t="str">
-        <v>No</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Any</v>
-      </c>
-      <c r="E4" t="str">
-        <v>backend/src/index.ts</v>
+    <row r="1" ht="20" customHeight="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" t="s">
+        <v>48</v>
+      </c>
+      <c r="I5" t="s">
+        <v>49</v>
+      </c>
+      <c r="J5" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" t="s">
+        <v>64</v>
+      </c>
+      <c r="I7" t="s">
+        <v>65</v>
+      </c>
+      <c r="J7" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F8" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I8" t="s">
+        <v>74</v>
+      </c>
+      <c r="J8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" t="s">
+        <v>79</v>
+      </c>
+      <c r="G9" t="s">
+        <v>80</v>
+      </c>
+      <c r="H9" t="s">
+        <v>81</v>
+      </c>
+      <c r="I9" t="s">
+        <v>82</v>
+      </c>
+      <c r="J9" t="s">
+        <v>21</v>
+      </c>
+      <c r="K9" t="s">
+        <v>22</v>
+      </c>
+      <c r="L9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G10" t="s">
+        <v>89</v>
+      </c>
+      <c r="H10" t="s">
+        <v>89</v>
+      </c>
+      <c r="I10" t="s">
+        <v>49</v>
+      </c>
+      <c r="J10" t="s">
+        <v>21</v>
+      </c>
+      <c r="K10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L10" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
-  </ignoredErrors>
+  <autoFilter ref="A1:L1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H20"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="35" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E5" t="s">
+        <v>113</v>
+      </c>
+      <c r="F5" t="s">
+        <v>114</v>
+      </c>
+      <c r="G5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E6" t="s">
+        <v>118</v>
+      </c>
+      <c r="F6" t="s">
+        <v>119</v>
+      </c>
+      <c r="G6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E7" t="s">
+        <v>123</v>
+      </c>
+      <c r="F7" t="s">
+        <v>124</v>
+      </c>
+      <c r="G7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" t="s">
+        <v>128</v>
+      </c>
+      <c r="G8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B9" t="s">
+        <v>122</v>
+      </c>
+      <c r="C9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" t="s">
+        <v>131</v>
+      </c>
+      <c r="E9" t="s">
+        <v>132</v>
+      </c>
+      <c r="F9" t="s">
+        <v>133</v>
+      </c>
+      <c r="G9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>135</v>
+      </c>
+      <c r="B10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" t="s">
+        <v>131</v>
+      </c>
+      <c r="E10" t="s">
+        <v>136</v>
+      </c>
+      <c r="F10" t="s">
+        <v>137</v>
+      </c>
+      <c r="G10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>139</v>
+      </c>
+      <c r="B11" t="s">
+        <v>122</v>
+      </c>
+      <c r="C11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D11" t="s">
+        <v>131</v>
+      </c>
+      <c r="E11" t="s">
+        <v>140</v>
+      </c>
+      <c r="F11" t="s">
+        <v>141</v>
+      </c>
+      <c r="G11" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>143</v>
+      </c>
+      <c r="B12" t="s">
+        <v>96</v>
+      </c>
+      <c r="C12" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" t="s">
+        <v>131</v>
+      </c>
+      <c r="E12" t="s">
+        <v>144</v>
+      </c>
+      <c r="F12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G12" t="s">
+        <v>21</v>
+      </c>
+      <c r="H12" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>147</v>
+      </c>
+      <c r="B13" t="s">
+        <v>122</v>
+      </c>
+      <c r="C13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D13" t="s">
+        <v>131</v>
+      </c>
+      <c r="E13" t="s">
+        <v>148</v>
+      </c>
+      <c r="F13" t="s">
+        <v>149</v>
+      </c>
+      <c r="G13" t="s">
+        <v>21</v>
+      </c>
+      <c r="H13" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>151</v>
+      </c>
+      <c r="B14" t="s">
+        <v>152</v>
+      </c>
+      <c r="C14" t="s">
+        <v>103</v>
+      </c>
+      <c r="D14" t="s">
+        <v>131</v>
+      </c>
+      <c r="E14" t="s">
+        <v>153</v>
+      </c>
+      <c r="F14" t="s">
+        <v>154</v>
+      </c>
+      <c r="G14" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>156</v>
+      </c>
+      <c r="B15" t="s">
+        <v>96</v>
+      </c>
+      <c r="C15" t="s">
+        <v>103</v>
+      </c>
+      <c r="D15" t="s">
+        <v>131</v>
+      </c>
+      <c r="E15" t="s">
+        <v>157</v>
+      </c>
+      <c r="F15" t="s">
+        <v>158</v>
+      </c>
+      <c r="G15" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>160</v>
+      </c>
+      <c r="B16" t="s">
+        <v>126</v>
+      </c>
+      <c r="C16" t="s">
+        <v>103</v>
+      </c>
+      <c r="D16" t="s">
+        <v>131</v>
+      </c>
+      <c r="E16" t="s">
+        <v>161</v>
+      </c>
+      <c r="F16" t="s">
+        <v>162</v>
+      </c>
+      <c r="G16" t="s">
+        <v>21</v>
+      </c>
+      <c r="H16" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" t="s">
+        <v>96</v>
+      </c>
+      <c r="C17" t="s">
+        <v>164</v>
+      </c>
+      <c r="D17" t="s">
+        <v>165</v>
+      </c>
+      <c r="E17" t="s">
+        <v>166</v>
+      </c>
+      <c r="F17" t="s">
+        <v>167</v>
+      </c>
+      <c r="G17" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>169</v>
+      </c>
+      <c r="B18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D18" t="s">
+        <v>104</v>
+      </c>
+      <c r="E18" t="s">
+        <v>170</v>
+      </c>
+      <c r="F18" t="s">
+        <v>171</v>
+      </c>
+      <c r="G18" t="s">
+        <v>21</v>
+      </c>
+      <c r="H18" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>173</v>
+      </c>
+      <c r="B19" t="s">
+        <v>122</v>
+      </c>
+      <c r="C19" t="s">
+        <v>97</v>
+      </c>
+      <c r="D19" t="s">
+        <v>98</v>
+      </c>
+      <c r="E19" t="s">
+        <v>174</v>
+      </c>
+      <c r="F19" t="s">
+        <v>175</v>
+      </c>
+      <c r="G19" t="s">
+        <v>21</v>
+      </c>
+      <c r="H19" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>177</v>
+      </c>
+      <c r="B20" t="s">
+        <v>122</v>
+      </c>
+      <c r="C20" t="s">
+        <v>97</v>
+      </c>
+      <c r="D20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E20" t="s">
+        <v>178</v>
+      </c>
+      <c r="F20" t="s">
+        <v>179</v>
+      </c>
+      <c r="G20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H20" t="s">
+        <v>180</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="35" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E2" t="s">
+        <v>188</v>
+      </c>
+      <c r="F2" t="s">
+        <v>189</v>
+      </c>
+      <c r="G2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F3" t="s">
+        <v>189</v>
+      </c>
+      <c r="G3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" t="s">
+        <v>187</v>
+      </c>
+      <c r="E4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F4" t="s">
+        <v>189</v>
+      </c>
+      <c r="G4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B5" t="s">
+        <v>198</v>
+      </c>
+      <c r="C5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" t="s">
+        <v>187</v>
+      </c>
+      <c r="E5" t="s">
+        <v>187</v>
+      </c>
+      <c r="F5" t="s">
+        <v>189</v>
+      </c>
+      <c r="G5" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>200</v>
+      </c>
+      <c r="B6" t="s">
+        <v>201</v>
+      </c>
+      <c r="C6" t="s">
+        <v>202</v>
+      </c>
+      <c r="D6" t="s">
+        <v>203</v>
+      </c>
+      <c r="E6" t="s">
+        <v>204</v>
+      </c>
+      <c r="F6" t="s">
+        <v>189</v>
+      </c>
+      <c r="G6" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>206</v>
+      </c>
+      <c r="B7" t="s">
+        <v>207</v>
+      </c>
+      <c r="C7" t="s">
+        <v>202</v>
+      </c>
+      <c r="D7" t="s">
+        <v>208</v>
+      </c>
+      <c r="E7" t="s">
+        <v>209</v>
+      </c>
+      <c r="F7" t="s">
+        <v>189</v>
+      </c>
+      <c r="G7" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>211</v>
+      </c>
+      <c r="B8" t="s">
+        <v>212</v>
+      </c>
+      <c r="C8" t="s">
+        <v>202</v>
+      </c>
+      <c r="D8" t="s">
+        <v>187</v>
+      </c>
+      <c r="E8" t="s">
+        <v>213</v>
+      </c>
+      <c r="F8" t="s">
+        <v>189</v>
+      </c>
+      <c r="G8" t="s">
+        <v>214</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B2">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>227</v>
+      </c>
+      <c r="B8" t="s">
+        <v>228</v>
+      </c>
+      <c r="C8" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>230</v>
+      </c>
+      <c r="B9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>232</v>
+      </c>
+      <c r="B10" t="s">
+        <v>233</v>
+      </c>
+      <c r="C10" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>237</v>
+      </c>
+      <c r="B13" t="s">
+        <v>238</v>
+      </c>
+      <c r="C13" t="s">
+        <v>239</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>